--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yeo.yeongfu\Desktop\app sjkc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34FB5964-D124-43F2-A6F1-9046A9D27541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF42527-6CC9-4C68-8033-08E9D27FFCB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{ED1B8368-D6B7-4B6C-9AFF-2ADDFA6ABAFC}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -20632,7 +20632,7 @@
             <v>正修国民型华文小学(一校)</v>
           </cell>
           <cell r="F13" t="str">
-            <v>KEK SIEW YAN</v>
+            <v>KUO WEI CHING</v>
           </cell>
         </row>
         <row r="14">
@@ -20719,8 +20719,8 @@
           <cell r="E21" t="str">
             <v>树人国民型华文小学</v>
           </cell>
-          <cell r="F21" t="str">
-            <v>KUO WEI CHING</v>
+          <cell r="F21" t="e">
+            <v>#N/A</v>
           </cell>
         </row>
         <row r="22">
@@ -20818,8 +20818,8 @@
           <cell r="E30" t="str">
             <v>同正国民型华文小学</v>
           </cell>
-          <cell r="F30" t="str">
-            <v>CHONG SIEW LING</v>
+          <cell r="F30" t="e">
+            <v>#N/A</v>
           </cell>
         </row>
         <row r="31">
@@ -21050,7 +21050,7 @@
             <v>培智国民型华文小学</v>
           </cell>
           <cell r="F51" t="str">
-            <v>CHANG AI TI</v>
+            <v>CHONG PEI ANN</v>
           </cell>
         </row>
         <row r="52">
@@ -21105,7 +21105,7 @@
             <v>圣若瑟国民型华文小学</v>
           </cell>
           <cell r="F56" t="str">
-            <v>CHONG PEI ANN</v>
+            <v>BONG MEE NGOH</v>
           </cell>
         </row>
         <row r="57">
@@ -21467,8 +21467,8 @@
           <cell r="E89" t="str">
             <v>古来国民型华文小学(二校)</v>
           </cell>
-          <cell r="F89" t="str">
-            <v>YONG SIEW LIN</v>
+          <cell r="F89" t="e">
+            <v>#N/A</v>
           </cell>
         </row>
         <row r="90">
@@ -21831,7 +21831,7 @@
             <v>益民国民型华文小学</v>
           </cell>
           <cell r="F122" t="str">
-            <v>TEO AH IMM</v>
+            <v>TAY SOON TECK</v>
           </cell>
         </row>
         <row r="123">
@@ -21908,7 +21908,7 @@
             <v>勤德国民型华文小学</v>
           </cell>
           <cell r="F129" t="str">
-            <v>CHUA LEE HUN</v>
+            <v>TEO AH IMM</v>
           </cell>
         </row>
         <row r="130">
@@ -21974,7 +21974,7 @@
             <v>林蒙国民型华文小学</v>
           </cell>
           <cell r="F135" t="str">
-            <v>TAY SOON TECK</v>
+            <v>CHUA LEE HUN</v>
           </cell>
         </row>
         <row r="136">
@@ -22238,7 +22238,7 @@
             <v>大同国民型华文小学</v>
           </cell>
           <cell r="F159" t="str">
-            <v>SOO YUAN HUN</v>
+            <v>JOANNE NG SIEW LING</v>
           </cell>
         </row>
         <row r="160">
@@ -22249,7 +22249,7 @@
             <v>培群一校国民型华文小学</v>
           </cell>
           <cell r="F160" t="str">
-            <v>BONG MEE NGOH</v>
+            <v>SOO YUAN HUN</v>
           </cell>
         </row>
         <row r="161">
@@ -22282,7 +22282,7 @@
             <v>乐育国民型华文小学</v>
           </cell>
           <cell r="F163" t="str">
-            <v>JOANNE NG SIEW LING</v>
+            <v>NG CHIEW WAN</v>
           </cell>
         </row>
         <row r="164">
@@ -22435,8 +22435,8 @@
           <cell r="E177" t="str">
             <v>乐育二校国民型华文小学</v>
           </cell>
-          <cell r="F177" t="str">
-            <v>NG CHIEW WAN</v>
+          <cell r="F177" t="e">
+            <v>#N/A</v>
           </cell>
         </row>
         <row r="178">
@@ -23225,20 +23225,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B25E2868-A279-45DE-AB1B-54D4EF298AFA}">
   <dimension ref="A1:L1000"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.54296875" customWidth="1"/>
-    <col min="3" max="4" width="22.1796875" customWidth="1"/>
-    <col min="5" max="5" width="5.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.453125" customWidth="1"/>
-    <col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.36328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.7265625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.1796875" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultColWidth="7" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
@@ -23415,7 +23402,7 @@
         <v>9</v>
       </c>
       <c r="F5" t="str">
-        <v>KEK SIEW YAN</v>
+        <v>KUO WEI CHING</v>
       </c>
       <c r="G5" t="s">
         <v>10</v>
@@ -24364,8 +24351,8 @@
       <c r="E30" t="s">
         <v>24</v>
       </c>
-      <c r="F30" t="str">
-        <v>KUO WEI CHING</v>
+      <c r="F30" t="e">
+        <v>#N/A</v>
       </c>
       <c r="G30" t="s">
         <v>29</v>
@@ -24440,8 +24427,8 @@
       <c r="E32" t="s">
         <v>24</v>
       </c>
-      <c r="F32" t="str">
-        <v>CHONG SIEW LING</v>
+      <c r="F32" t="e">
+        <v>#N/A</v>
       </c>
       <c r="G32" t="s">
         <v>10</v>
@@ -24859,7 +24846,7 @@
         <v>9</v>
       </c>
       <c r="F43" t="str">
-        <v>CHONG PEI ANN</v>
+        <v>BONG MEE NGOH</v>
       </c>
       <c r="G43" t="s">
         <v>10</v>
@@ -25239,7 +25226,7 @@
         <v>9</v>
       </c>
       <c r="F53" t="str">
-        <v>CHANG AI TI</v>
+        <v>CHONG PEI ANN</v>
       </c>
       <c r="G53" t="s">
         <v>10</v>
@@ -26872,8 +26859,8 @@
       <c r="E96" t="s">
         <v>44</v>
       </c>
-      <c r="F96" t="str">
-        <v>YONG SIEW LIN</v>
+      <c r="F96" t="e">
+        <v>#N/A</v>
       </c>
       <c r="G96" t="s">
         <v>29</v>
@@ -27291,7 +27278,7 @@
         <v>24</v>
       </c>
       <c r="F107" t="str">
-        <v>TEO AH IMM</v>
+        <v>TAY SOON TECK</v>
       </c>
       <c r="G107" t="s">
         <v>10</v>
@@ -27443,7 +27430,7 @@
         <v>24</v>
       </c>
       <c r="F111" t="str">
-        <v>CHUA LEE HUN</v>
+        <v>TEO AH IMM</v>
       </c>
       <c r="G111" t="s">
         <v>10</v>
@@ -27823,7 +27810,7 @@
         <v>24</v>
       </c>
       <c r="F121" t="str">
-        <v>TAY SOON TECK</v>
+        <v>CHUA LEE HUN</v>
       </c>
       <c r="G121" t="s">
         <v>10</v>
@@ -29457,7 +29444,7 @@
         <v>24</v>
       </c>
       <c r="F164" t="str">
-        <v>JOANNE NG SIEW LING</v>
+        <v>NG CHIEW WAN</v>
       </c>
       <c r="G164" t="s">
         <v>29</v>
@@ -29532,8 +29519,8 @@
       <c r="E166" t="s">
         <v>24</v>
       </c>
-      <c r="F166" t="str">
-        <v>NG CHIEW WAN</v>
+      <c r="F166" t="e">
+        <v>#N/A</v>
       </c>
       <c r="G166" t="s">
         <v>10</v>
@@ -29761,7 +29748,7 @@
         <v>9</v>
       </c>
       <c r="F172" t="str">
-        <v>BONG MEE NGOH</v>
+        <v>SOO YUAN HUN</v>
       </c>
       <c r="G172" t="s">
         <v>10</v>
@@ -29913,7 +29900,7 @@
         <v>9</v>
       </c>
       <c r="F176" t="str">
-        <v>SOO YUAN HUN</v>
+        <v>JOANNE NG SIEW LING</v>
       </c>
       <c r="G176" t="s">
         <v>10</v>
